--- a/artfynd/A 56687-2025 artfynd.xlsx
+++ b/artfynd/A 56687-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -806,6 +806,2260 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129800360</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98752</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Väntinge 2:1 (2) (A 56687-2025), Gtl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>700467</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6365717</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med enstaka kalkblock.</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129800414</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98752</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Väntinge 2:1 (2) (A 56687-2025), Gtl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>700392</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6365598</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med enstaka kalkblock. Skogen tidigare plockhuggen med avverkningsstråk.</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129800392</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98808</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Väntinge 2:1 (2) (A 56687-2025), Gtl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>700427</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6365490</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med enstaka kalkblock. Skogen tidigare plockhuggen med avverkningsstråk.</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129800376</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98752</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Väntinge 2:1 (2) (A 56687-2025), Gtl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>700451</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6365624</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med enstaka kalkblock.</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129800400</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98752</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Väntinge 2:1 (2) (A 56687-2025), Gtl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>700388</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6365480</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med enstaka kalkblock. Skogen tidigare plockhuggen med avverkningsstråk.</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129800387</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98752</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Väntinge 2:1 (2) (A 56687-2025), Gtl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>700434</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6365543</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med enstaka kalkblock. Skogen tidigare plockhuggen med avverkningsstråk.</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129800363</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98752</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Väntinge 2:1 (2) (A 56687-2025), Gtl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>700481</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6365698</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med enstaka kalkblock.</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129800379</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98752</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Väntinge 2:1 (2) (A 56687-2025), Gtl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>700431</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6365585</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med enstaka kalkblock. Skogen tidigare plockhuggen med avverkningsstråk.</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129800557</v>
+      </c>
+      <c r="B11" t="n">
+        <v>96370</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Väntinge 2:1 (2) (A 56687-2025), Gtl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>700398</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6365612</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129800406</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98752</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Väntinge 2:1 (2) (A 56687-2025), Gtl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>700397</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6365538</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med enstaka kalkblock. Skogen tidigare plockhuggen med avverkningsstråk.</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129800393</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98752</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Väntinge 2:1 (2) (A 56687-2025), Gtl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>700427</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6365490</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med enstaka kalkblock. Skogen tidigare plockhuggen med avverkningsstråk.</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129800409</v>
+      </c>
+      <c r="B14" t="n">
+        <v>104257</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220164</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Solvända</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Väntinge 2:1 (2) (A 56687-2025), Gtl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>700391</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6365579</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med enstaka kalkblock. Skogen tidigare plockhuggen med avverkningsstråk.</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129800410</v>
+      </c>
+      <c r="B15" t="n">
+        <v>107103</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Väntinge 2:1 (2) (A 56687-2025), Gtl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>700391</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6365579</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med enstaka kalkblock. Skogen tidigare plockhuggen med avverkningsstråk.</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129800403</v>
+      </c>
+      <c r="B16" t="n">
+        <v>107103</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Väntinge 2:1 (2) (A 56687-2025), Gtl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>700398</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6365502</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med enstaka kalkblock. Skogen tidigare plockhuggen med avverkningsstråk.</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129800367</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98752</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Väntinge 2:1 (2) (A 56687-2025), Gtl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>700469</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6365674</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med enstaka kalkblock.</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129800389</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98752</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Väntinge 2:1 (2) (A 56687-2025), Gtl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>700432</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6365511</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med enstaka kalkblock. Skogen tidigare plockhuggen med avverkningsstråk.</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129800345</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98808</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Väntinge 2:1 (2) (A 56687-2025), Gtl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>700433</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6365700</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kalkglänta.</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129800349</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98776</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Väntinge 2:1 (2) (A 56687-2025), Gtl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>700411</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6365728</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kalkglänta.</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129800385</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98752</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Väntinge 2:1 (2) (A 56687-2025), Gtl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>700433</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6365521</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med enstaka kalkblock. Skogen tidigare plockhuggen med avverkningsstråk.</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129800366</v>
+      </c>
+      <c r="B22" t="n">
+        <v>107103</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Väntinge 2:1 (2) (A 56687-2025), Gtl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>700478</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6365684</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med enstaka kalkblock.</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56687-2025 artfynd.xlsx
+++ b/artfynd/A 56687-2025 artfynd.xlsx
@@ -809,10 +809,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129800360</v>
+        <v>129800392</v>
       </c>
       <c r="B3" t="n">
-        <v>98752</v>
+        <v>98808</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,26 +820,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219798</v>
+        <v>219874</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -858,10 +858,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>700467</v>
+        <v>700427</v>
       </c>
       <c r="R3" t="n">
-        <v>6365717</v>
+        <v>6365490</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -907,7 +907,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med enstaka kalkblock.</t>
+          <t>Kalkbarrskog med enstaka kalkblock. Skogen tidigare plockhuggen med avverkningsstråk.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -925,7 +925,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129800414</v>
+        <v>129800376</v>
       </c>
       <c r="B4" t="n">
         <v>98752</v>
@@ -955,7 +955,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -974,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>700392</v>
+        <v>700451</v>
       </c>
       <c r="R4" t="n">
-        <v>6365598</v>
+        <v>6365624</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med enstaka kalkblock. Skogen tidigare plockhuggen med avverkningsstråk.</t>
+          <t>Kalkbarrskog med enstaka kalkblock.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1041,10 +1041,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129800392</v>
+        <v>129800360</v>
       </c>
       <c r="B5" t="n">
-        <v>98808</v>
+        <v>98752</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1052,26 +1052,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219874</v>
+        <v>219798</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1090,10 +1090,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>700427</v>
+        <v>700467</v>
       </c>
       <c r="R5" t="n">
-        <v>6365490</v>
+        <v>6365717</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med enstaka kalkblock. Skogen tidigare plockhuggen med avverkningsstråk.</t>
+          <t>Kalkbarrskog med enstaka kalkblock.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1157,7 +1157,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129800376</v>
+        <v>129800414</v>
       </c>
       <c r="B6" t="n">
         <v>98752</v>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>700451</v>
+        <v>700392</v>
       </c>
       <c r="R6" t="n">
-        <v>6365624</v>
+        <v>6365598</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med enstaka kalkblock.</t>
+          <t>Kalkbarrskog med enstaka kalkblock. Skogen tidigare plockhuggen med avverkningsstråk.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -2075,10 +2075,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129800409</v>
+        <v>129800410</v>
       </c>
       <c r="B14" t="n">
-        <v>104257</v>
+        <v>107103</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2086,21 +2086,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220164</v>
+        <v>221849</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2177,10 +2177,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129800410</v>
+        <v>129800409</v>
       </c>
       <c r="B15" t="n">
-        <v>107103</v>
+        <v>104257</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2188,21 +2188,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2279,45 +2279,59 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129800403</v>
+        <v>129800367</v>
       </c>
       <c r="B16" t="n">
-        <v>107103</v>
+        <v>98752</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221849</v>
+        <v>219798</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Väntinge 2:1 (2) (A 56687-2025), Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>700398</v>
+        <v>700469</v>
       </c>
       <c r="R16" t="n">
-        <v>6365502</v>
+        <v>6365674</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2363,7 +2377,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med enstaka kalkblock. Skogen tidigare plockhuggen med avverkningsstråk.</t>
+          <t>Kalkbarrskog med enstaka kalkblock.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2381,59 +2395,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129800367</v>
+        <v>129800403</v>
       </c>
       <c r="B17" t="n">
-        <v>98752</v>
+        <v>107103</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219798</v>
+        <v>221849</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Väntinge 2:1 (2) (A 56687-2025), Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>700469</v>
+        <v>700398</v>
       </c>
       <c r="R17" t="n">
-        <v>6365674</v>
+        <v>6365502</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med enstaka kalkblock.</t>
+          <t>Kalkbarrskog med enstaka kalkblock. Skogen tidigare plockhuggen med avverkningsstråk.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>

--- a/artfynd/A 56687-2025 artfynd.xlsx
+++ b/artfynd/A 56687-2025 artfynd.xlsx
@@ -1621,10 +1621,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129800379</v>
+        <v>129800557</v>
       </c>
       <c r="B10" t="n">
-        <v>98752</v>
+        <v>96370</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,36 +1632,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219798</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1670,10 +1665,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>700431</v>
+        <v>700398</v>
       </c>
       <c r="R10" t="n">
-        <v>6365585</v>
+        <v>6365612</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1716,11 +1711,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog med enstaka kalkblock. Skogen tidigare plockhuggen med avverkningsstråk.</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1737,10 +1727,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129800557</v>
+        <v>129800379</v>
       </c>
       <c r="B11" t="n">
-        <v>96370</v>
+        <v>98752</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,31 +1738,36 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>219798</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1781,10 +1776,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>700398</v>
+        <v>700431</v>
       </c>
       <c r="R11" t="n">
-        <v>6365612</v>
+        <v>6365585</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1827,6 +1822,11 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med enstaka kalkblock. Skogen tidigare plockhuggen med avverkningsstråk.</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -2075,10 +2075,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129800410</v>
+        <v>129800409</v>
       </c>
       <c r="B14" t="n">
-        <v>107103</v>
+        <v>104257</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2086,21 +2086,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2177,10 +2177,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129800409</v>
+        <v>129800410</v>
       </c>
       <c r="B15" t="n">
-        <v>104257</v>
+        <v>107103</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2188,21 +2188,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220164</v>
+        <v>221849</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>

--- a/artfynd/A 56687-2025 artfynd.xlsx
+++ b/artfynd/A 56687-2025 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>129800392</v>
       </c>
       <c r="B3" t="n">
-        <v>98808</v>
+        <v>98812</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         <v>129800376</v>
       </c>
       <c r="B4" t="n">
-        <v>98752</v>
+        <v>98756</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>129800360</v>
       </c>
       <c r="B5" t="n">
-        <v>98752</v>
+        <v>98756</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>129800414</v>
       </c>
       <c r="B6" t="n">
-        <v>98752</v>
+        <v>98756</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>129800400</v>
       </c>
       <c r="B7" t="n">
-        <v>98752</v>
+        <v>98756</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>129800387</v>
       </c>
       <c r="B8" t="n">
-        <v>98752</v>
+        <v>98756</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>129800363</v>
       </c>
       <c r="B9" t="n">
-        <v>98752</v>
+        <v>98756</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>129800557</v>
       </c>
       <c r="B10" t="n">
-        <v>96370</v>
+        <v>96374</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>129800379</v>
       </c>
       <c r="B11" t="n">
-        <v>98752</v>
+        <v>98756</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>129800406</v>
       </c>
       <c r="B12" t="n">
-        <v>98752</v>
+        <v>98756</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>129800393</v>
       </c>
       <c r="B13" t="n">
-        <v>98752</v>
+        <v>98756</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>129800409</v>
       </c>
       <c r="B14" t="n">
-        <v>104257</v>
+        <v>104261</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>129800410</v>
       </c>
       <c r="B15" t="n">
-        <v>107103</v>
+        <v>107107</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
         <v>129800367</v>
       </c>
       <c r="B16" t="n">
-        <v>98752</v>
+        <v>98756</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>129800403</v>
       </c>
       <c r="B17" t="n">
-        <v>107103</v>
+        <v>107107</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         <v>129800389</v>
       </c>
       <c r="B18" t="n">
-        <v>98752</v>
+        <v>98756</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>129800345</v>
       </c>
       <c r="B19" t="n">
-        <v>98808</v>
+        <v>98812</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>129800349</v>
       </c>
       <c r="B20" t="n">
-        <v>98776</v>
+        <v>98780</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>129800385</v>
       </c>
       <c r="B21" t="n">
-        <v>98752</v>
+        <v>98756</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>129800366</v>
       </c>
       <c r="B22" t="n">
-        <v>107103</v>
+        <v>107107</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 56687-2025 artfynd.xlsx
+++ b/artfynd/A 56687-2025 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>129800392</v>
       </c>
       <c r="B3" t="n">
-        <v>98812</v>
+        <v>98814</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         <v>129800376</v>
       </c>
       <c r="B4" t="n">
-        <v>98756</v>
+        <v>98758</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>129800360</v>
       </c>
       <c r="B5" t="n">
-        <v>98756</v>
+        <v>98758</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>129800414</v>
       </c>
       <c r="B6" t="n">
-        <v>98756</v>
+        <v>98758</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>129800400</v>
       </c>
       <c r="B7" t="n">
-        <v>98756</v>
+        <v>98758</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>129800387</v>
       </c>
       <c r="B8" t="n">
-        <v>98756</v>
+        <v>98758</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>129800363</v>
       </c>
       <c r="B9" t="n">
-        <v>98756</v>
+        <v>98758</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>129800557</v>
       </c>
       <c r="B10" t="n">
-        <v>96374</v>
+        <v>96376</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>129800379</v>
       </c>
       <c r="B11" t="n">
-        <v>98756</v>
+        <v>98758</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>129800406</v>
       </c>
       <c r="B12" t="n">
-        <v>98756</v>
+        <v>98758</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>129800393</v>
       </c>
       <c r="B13" t="n">
-        <v>98756</v>
+        <v>98758</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>129800409</v>
       </c>
       <c r="B14" t="n">
-        <v>104261</v>
+        <v>104263</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>129800410</v>
       </c>
       <c r="B15" t="n">
-        <v>107107</v>
+        <v>107109</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
         <v>129800367</v>
       </c>
       <c r="B16" t="n">
-        <v>98756</v>
+        <v>98758</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>129800403</v>
       </c>
       <c r="B17" t="n">
-        <v>107107</v>
+        <v>107109</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         <v>129800389</v>
       </c>
       <c r="B18" t="n">
-        <v>98756</v>
+        <v>98758</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>129800345</v>
       </c>
       <c r="B19" t="n">
-        <v>98812</v>
+        <v>98814</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>129800349</v>
       </c>
       <c r="B20" t="n">
-        <v>98780</v>
+        <v>98782</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2845,59 +2845,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129800385</v>
+        <v>129800366</v>
       </c>
       <c r="B21" t="n">
-        <v>98756</v>
+        <v>107109</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219798</v>
+        <v>221849</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Väntinge 2:1 (2) (A 56687-2025), Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>700433</v>
+        <v>700478</v>
       </c>
       <c r="R21" t="n">
-        <v>6365521</v>
+        <v>6365684</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2943,7 +2929,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med enstaka kalkblock. Skogen tidigare plockhuggen med avverkningsstråk.</t>
+          <t>Kalkbarrskog med enstaka kalkblock.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2961,45 +2947,59 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129800366</v>
+        <v>129800385</v>
       </c>
       <c r="B22" t="n">
-        <v>107107</v>
+        <v>98758</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221849</v>
+        <v>219798</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Väntinge 2:1 (2) (A 56687-2025), Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>700478</v>
+        <v>700433</v>
       </c>
       <c r="R22" t="n">
-        <v>6365684</v>
+        <v>6365521</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med enstaka kalkblock.</t>
+          <t>Kalkbarrskog med enstaka kalkblock. Skogen tidigare plockhuggen med avverkningsstråk.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>

--- a/artfynd/A 56687-2025 artfynd.xlsx
+++ b/artfynd/A 56687-2025 artfynd.xlsx
@@ -1621,10 +1621,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129800557</v>
+        <v>129800379</v>
       </c>
       <c r="B10" t="n">
-        <v>96376</v>
+        <v>98758</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,31 +1632,36 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>219798</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1665,10 +1670,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>700398</v>
+        <v>700431</v>
       </c>
       <c r="R10" t="n">
-        <v>6365612</v>
+        <v>6365585</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1711,6 +1716,11 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med enstaka kalkblock. Skogen tidigare plockhuggen med avverkningsstråk.</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1727,10 +1737,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129800379</v>
+        <v>129800557</v>
       </c>
       <c r="B11" t="n">
-        <v>98758</v>
+        <v>96376</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,36 +1748,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219798</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1776,10 +1781,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>700431</v>
+        <v>700398</v>
       </c>
       <c r="R11" t="n">
-        <v>6365585</v>
+        <v>6365612</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1822,11 +1827,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog med enstaka kalkblock. Skogen tidigare plockhuggen med avverkningsstråk.</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -2845,45 +2845,59 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129800366</v>
+        <v>129800385</v>
       </c>
       <c r="B21" t="n">
-        <v>107109</v>
+        <v>98758</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221849</v>
+        <v>219798</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Väntinge 2:1 (2) (A 56687-2025), Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>700478</v>
+        <v>700433</v>
       </c>
       <c r="R21" t="n">
-        <v>6365684</v>
+        <v>6365521</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2929,7 +2943,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med enstaka kalkblock.</t>
+          <t>Kalkbarrskog med enstaka kalkblock. Skogen tidigare plockhuggen med avverkningsstråk.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2947,59 +2961,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129800385</v>
+        <v>129800366</v>
       </c>
       <c r="B22" t="n">
-        <v>98758</v>
+        <v>107109</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219798</v>
+        <v>221849</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Väntinge 2:1 (2) (A 56687-2025), Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>700433</v>
+        <v>700478</v>
       </c>
       <c r="R22" t="n">
-        <v>6365521</v>
+        <v>6365684</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med enstaka kalkblock. Skogen tidigare plockhuggen med avverkningsstråk.</t>
+          <t>Kalkbarrskog med enstaka kalkblock.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>

--- a/artfynd/A 56687-2025 artfynd.xlsx
+++ b/artfynd/A 56687-2025 artfynd.xlsx
@@ -1041,7 +1041,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129800360</v>
+        <v>129800414</v>
       </c>
       <c r="B5" t="n">
         <v>98758</v>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1090,10 +1090,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>700467</v>
+        <v>700392</v>
       </c>
       <c r="R5" t="n">
-        <v>6365717</v>
+        <v>6365598</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med enstaka kalkblock.</t>
+          <t>Kalkbarrskog med enstaka kalkblock. Skogen tidigare plockhuggen med avverkningsstråk.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1157,7 +1157,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129800414</v>
+        <v>129800360</v>
       </c>
       <c r="B6" t="n">
         <v>98758</v>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>700392</v>
+        <v>700467</v>
       </c>
       <c r="R6" t="n">
-        <v>6365598</v>
+        <v>6365717</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med enstaka kalkblock. Skogen tidigare plockhuggen med avverkningsstråk.</t>
+          <t>Kalkbarrskog med enstaka kalkblock.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -2845,59 +2845,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129800385</v>
+        <v>129800366</v>
       </c>
       <c r="B21" t="n">
-        <v>98758</v>
+        <v>107109</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219798</v>
+        <v>221849</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Väntinge 2:1 (2) (A 56687-2025), Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>700433</v>
+        <v>700478</v>
       </c>
       <c r="R21" t="n">
-        <v>6365521</v>
+        <v>6365684</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2943,7 +2929,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med enstaka kalkblock. Skogen tidigare plockhuggen med avverkningsstråk.</t>
+          <t>Kalkbarrskog med enstaka kalkblock.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2961,45 +2947,59 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129800366</v>
+        <v>129800385</v>
       </c>
       <c r="B22" t="n">
-        <v>107109</v>
+        <v>98758</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221849</v>
+        <v>219798</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Väntinge 2:1 (2) (A 56687-2025), Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>700478</v>
+        <v>700433</v>
       </c>
       <c r="R22" t="n">
-        <v>6365684</v>
+        <v>6365521</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med enstaka kalkblock.</t>
+          <t>Kalkbarrskog med enstaka kalkblock. Skogen tidigare plockhuggen med avverkningsstråk.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>

--- a/artfynd/A 56687-2025 artfynd.xlsx
+++ b/artfynd/A 56687-2025 artfynd.xlsx
@@ -2845,45 +2845,59 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129800366</v>
+        <v>129800385</v>
       </c>
       <c r="B21" t="n">
-        <v>107109</v>
+        <v>98758</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221849</v>
+        <v>219798</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Väntinge 2:1 (2) (A 56687-2025), Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>700478</v>
+        <v>700433</v>
       </c>
       <c r="R21" t="n">
-        <v>6365684</v>
+        <v>6365521</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2929,7 +2943,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med enstaka kalkblock.</t>
+          <t>Kalkbarrskog med enstaka kalkblock. Skogen tidigare plockhuggen med avverkningsstråk.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2947,59 +2961,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129800385</v>
+        <v>129800366</v>
       </c>
       <c r="B22" t="n">
-        <v>98758</v>
+        <v>107109</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219798</v>
+        <v>221849</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Väntinge 2:1 (2) (A 56687-2025), Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>700433</v>
+        <v>700478</v>
       </c>
       <c r="R22" t="n">
-        <v>6365521</v>
+        <v>6365684</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med enstaka kalkblock. Skogen tidigare plockhuggen med avverkningsstråk.</t>
+          <t>Kalkbarrskog med enstaka kalkblock.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>

--- a/artfynd/A 56687-2025 artfynd.xlsx
+++ b/artfynd/A 56687-2025 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>129800392</v>
       </c>
       <c r="B3" t="n">
-        <v>98814</v>
+        <v>98824</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         <v>129800376</v>
       </c>
       <c r="B4" t="n">
-        <v>98758</v>
+        <v>98768</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1041,10 +1041,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129800414</v>
+        <v>129800360</v>
       </c>
       <c r="B5" t="n">
-        <v>98758</v>
+        <v>98768</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1090,10 +1090,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>700392</v>
+        <v>700467</v>
       </c>
       <c r="R5" t="n">
-        <v>6365598</v>
+        <v>6365717</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med enstaka kalkblock. Skogen tidigare plockhuggen med avverkningsstråk.</t>
+          <t>Kalkbarrskog med enstaka kalkblock.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1157,10 +1157,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129800360</v>
+        <v>129800414</v>
       </c>
       <c r="B6" t="n">
-        <v>98758</v>
+        <v>98768</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>700467</v>
+        <v>700392</v>
       </c>
       <c r="R6" t="n">
-        <v>6365717</v>
+        <v>6365598</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med enstaka kalkblock.</t>
+          <t>Kalkbarrskog med enstaka kalkblock. Skogen tidigare plockhuggen med avverkningsstråk.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1276,7 +1276,7 @@
         <v>129800400</v>
       </c>
       <c r="B7" t="n">
-        <v>98758</v>
+        <v>98768</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>129800387</v>
       </c>
       <c r="B8" t="n">
-        <v>98758</v>
+        <v>98768</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>129800363</v>
       </c>
       <c r="B9" t="n">
-        <v>98758</v>
+        <v>98768</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1621,10 +1621,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129800379</v>
+        <v>129800557</v>
       </c>
       <c r="B10" t="n">
-        <v>98758</v>
+        <v>96386</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,36 +1632,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219798</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1670,10 +1665,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>700431</v>
+        <v>700398</v>
       </c>
       <c r="R10" t="n">
-        <v>6365585</v>
+        <v>6365612</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1716,11 +1711,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog med enstaka kalkblock. Skogen tidigare plockhuggen med avverkningsstråk.</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1737,10 +1727,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129800557</v>
+        <v>129800379</v>
       </c>
       <c r="B11" t="n">
-        <v>96376</v>
+        <v>98768</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,31 +1738,36 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>219798</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1781,10 +1776,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>700398</v>
+        <v>700431</v>
       </c>
       <c r="R11" t="n">
-        <v>6365612</v>
+        <v>6365585</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1827,6 +1822,11 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med enstaka kalkblock. Skogen tidigare plockhuggen med avverkningsstråk.</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1846,7 +1846,7 @@
         <v>129800406</v>
       </c>
       <c r="B12" t="n">
-        <v>98758</v>
+        <v>98768</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>129800393</v>
       </c>
       <c r="B13" t="n">
-        <v>98758</v>
+        <v>98768</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>129800409</v>
       </c>
       <c r="B14" t="n">
-        <v>104263</v>
+        <v>104273</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>129800410</v>
       </c>
       <c r="B15" t="n">
-        <v>107109</v>
+        <v>107119</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2279,59 +2279,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129800367</v>
+        <v>129800403</v>
       </c>
       <c r="B16" t="n">
-        <v>98758</v>
+        <v>107119</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219798</v>
+        <v>221849</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Väntinge 2:1 (2) (A 56687-2025), Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>700469</v>
+        <v>700398</v>
       </c>
       <c r="R16" t="n">
-        <v>6365674</v>
+        <v>6365502</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2377,7 +2363,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med enstaka kalkblock.</t>
+          <t>Kalkbarrskog med enstaka kalkblock. Skogen tidigare plockhuggen med avverkningsstråk.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2395,45 +2381,59 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129800403</v>
+        <v>129800367</v>
       </c>
       <c r="B17" t="n">
-        <v>107109</v>
+        <v>98768</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221849</v>
+        <v>219798</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Väntinge 2:1 (2) (A 56687-2025), Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>700398</v>
+        <v>700469</v>
       </c>
       <c r="R17" t="n">
-        <v>6365502</v>
+        <v>6365674</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med enstaka kalkblock. Skogen tidigare plockhuggen med avverkningsstråk.</t>
+          <t>Kalkbarrskog med enstaka kalkblock.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2500,7 +2500,7 @@
         <v>129800389</v>
       </c>
       <c r="B18" t="n">
-        <v>98758</v>
+        <v>98768</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>129800345</v>
       </c>
       <c r="B19" t="n">
-        <v>98814</v>
+        <v>98824</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>129800349</v>
       </c>
       <c r="B20" t="n">
-        <v>98782</v>
+        <v>98792</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2845,59 +2845,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129800385</v>
+        <v>129800366</v>
       </c>
       <c r="B21" t="n">
-        <v>98758</v>
+        <v>107119</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219798</v>
+        <v>221849</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Väntinge 2:1 (2) (A 56687-2025), Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>700433</v>
+        <v>700478</v>
       </c>
       <c r="R21" t="n">
-        <v>6365521</v>
+        <v>6365684</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2943,7 +2929,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med enstaka kalkblock. Skogen tidigare plockhuggen med avverkningsstråk.</t>
+          <t>Kalkbarrskog med enstaka kalkblock.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2961,45 +2947,59 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129800366</v>
+        <v>129800385</v>
       </c>
       <c r="B22" t="n">
-        <v>107109</v>
+        <v>98768</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221849</v>
+        <v>219798</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Väntinge 2:1 (2) (A 56687-2025), Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>700478</v>
+        <v>700433</v>
       </c>
       <c r="R22" t="n">
-        <v>6365684</v>
+        <v>6365521</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med enstaka kalkblock.</t>
+          <t>Kalkbarrskog med enstaka kalkblock. Skogen tidigare plockhuggen med avverkningsstråk.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>

--- a/artfynd/A 56687-2025 artfynd.xlsx
+++ b/artfynd/A 56687-2025 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>129800392</v>
       </c>
       <c r="B3" t="n">
-        <v>98824</v>
+        <v>98828</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         <v>129800376</v>
       </c>
       <c r="B4" t="n">
-        <v>98768</v>
+        <v>98772</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>129800360</v>
       </c>
       <c r="B5" t="n">
-        <v>98768</v>
+        <v>98772</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>129800414</v>
       </c>
       <c r="B6" t="n">
-        <v>98768</v>
+        <v>98772</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>129800400</v>
       </c>
       <c r="B7" t="n">
-        <v>98768</v>
+        <v>98772</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>129800387</v>
       </c>
       <c r="B8" t="n">
-        <v>98768</v>
+        <v>98772</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>129800363</v>
       </c>
       <c r="B9" t="n">
-        <v>98768</v>
+        <v>98772</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>129800557</v>
       </c>
       <c r="B10" t="n">
-        <v>96386</v>
+        <v>96390</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>129800379</v>
       </c>
       <c r="B11" t="n">
-        <v>98768</v>
+        <v>98772</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>129800406</v>
       </c>
       <c r="B12" t="n">
-        <v>98768</v>
+        <v>98772</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>129800393</v>
       </c>
       <c r="B13" t="n">
-        <v>98768</v>
+        <v>98772</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>129800409</v>
       </c>
       <c r="B14" t="n">
-        <v>104273</v>
+        <v>104277</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>129800410</v>
       </c>
       <c r="B15" t="n">
-        <v>107119</v>
+        <v>107123</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2279,45 +2279,59 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129800403</v>
+        <v>129800367</v>
       </c>
       <c r="B16" t="n">
-        <v>107119</v>
+        <v>98772</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221849</v>
+        <v>219798</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Väntinge 2:1 (2) (A 56687-2025), Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>700398</v>
+        <v>700469</v>
       </c>
       <c r="R16" t="n">
-        <v>6365502</v>
+        <v>6365674</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2363,7 +2377,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med enstaka kalkblock. Skogen tidigare plockhuggen med avverkningsstråk.</t>
+          <t>Kalkbarrskog med enstaka kalkblock.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2381,59 +2395,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129800367</v>
+        <v>129800403</v>
       </c>
       <c r="B17" t="n">
-        <v>98768</v>
+        <v>107123</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219798</v>
+        <v>221849</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Väntinge 2:1 (2) (A 56687-2025), Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>700469</v>
+        <v>700398</v>
       </c>
       <c r="R17" t="n">
-        <v>6365674</v>
+        <v>6365502</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med enstaka kalkblock.</t>
+          <t>Kalkbarrskog med enstaka kalkblock. Skogen tidigare plockhuggen med avverkningsstråk.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2500,7 +2500,7 @@
         <v>129800389</v>
       </c>
       <c r="B18" t="n">
-        <v>98768</v>
+        <v>98772</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>129800345</v>
       </c>
       <c r="B19" t="n">
-        <v>98824</v>
+        <v>98828</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>129800349</v>
       </c>
       <c r="B20" t="n">
-        <v>98792</v>
+        <v>98796</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>129800366</v>
       </c>
       <c r="B21" t="n">
-        <v>107119</v>
+        <v>107123</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>129800385</v>
       </c>
       <c r="B22" t="n">
-        <v>98768</v>
+        <v>98772</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 56687-2025 artfynd.xlsx
+++ b/artfynd/A 56687-2025 artfynd.xlsx
@@ -2845,45 +2845,59 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129800366</v>
+        <v>129800385</v>
       </c>
       <c r="B21" t="n">
-        <v>107123</v>
+        <v>98772</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221849</v>
+        <v>219798</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Väntinge 2:1 (2) (A 56687-2025), Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>700478</v>
+        <v>700433</v>
       </c>
       <c r="R21" t="n">
-        <v>6365684</v>
+        <v>6365521</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2929,7 +2943,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med enstaka kalkblock.</t>
+          <t>Kalkbarrskog med enstaka kalkblock. Skogen tidigare plockhuggen med avverkningsstråk.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2947,59 +2961,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129800385</v>
+        <v>129800366</v>
       </c>
       <c r="B22" t="n">
-        <v>98772</v>
+        <v>107123</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219798</v>
+        <v>221849</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Väntinge 2:1 (2) (A 56687-2025), Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>700433</v>
+        <v>700478</v>
       </c>
       <c r="R22" t="n">
-        <v>6365521</v>
+        <v>6365684</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med enstaka kalkblock. Skogen tidigare plockhuggen med avverkningsstråk.</t>
+          <t>Kalkbarrskog med enstaka kalkblock.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>

--- a/artfynd/A 56687-2025 artfynd.xlsx
+++ b/artfynd/A 56687-2025 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>129800392</v>
       </c>
       <c r="B3" t="n">
-        <v>98828</v>
+        <v>98831</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         <v>129800376</v>
       </c>
       <c r="B4" t="n">
-        <v>98772</v>
+        <v>98775</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>129800360</v>
       </c>
       <c r="B5" t="n">
-        <v>98772</v>
+        <v>98775</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>129800414</v>
       </c>
       <c r="B6" t="n">
-        <v>98772</v>
+        <v>98775</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>129800400</v>
       </c>
       <c r="B7" t="n">
-        <v>98772</v>
+        <v>98775</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>129800387</v>
       </c>
       <c r="B8" t="n">
-        <v>98772</v>
+        <v>98775</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>129800363</v>
       </c>
       <c r="B9" t="n">
-        <v>98772</v>
+        <v>98775</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1621,10 +1621,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129800557</v>
+        <v>129800379</v>
       </c>
       <c r="B10" t="n">
-        <v>96390</v>
+        <v>98775</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,31 +1632,36 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>219798</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1665,10 +1670,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>700398</v>
+        <v>700431</v>
       </c>
       <c r="R10" t="n">
-        <v>6365612</v>
+        <v>6365585</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1711,6 +1716,11 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med enstaka kalkblock. Skogen tidigare plockhuggen med avverkningsstråk.</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1727,10 +1737,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129800379</v>
+        <v>129800557</v>
       </c>
       <c r="B11" t="n">
-        <v>98772</v>
+        <v>96393</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,36 +1748,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219798</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1776,10 +1781,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>700431</v>
+        <v>700398</v>
       </c>
       <c r="R11" t="n">
-        <v>6365585</v>
+        <v>6365612</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1822,11 +1827,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog med enstaka kalkblock. Skogen tidigare plockhuggen med avverkningsstråk.</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1846,7 +1846,7 @@
         <v>129800406</v>
       </c>
       <c r="B12" t="n">
-        <v>98772</v>
+        <v>98775</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>129800393</v>
       </c>
       <c r="B13" t="n">
-        <v>98772</v>
+        <v>98775</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,10 +2075,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129800409</v>
+        <v>129800410</v>
       </c>
       <c r="B14" t="n">
-        <v>104277</v>
+        <v>107126</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2086,21 +2086,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220164</v>
+        <v>221849</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2177,10 +2177,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129800410</v>
+        <v>129800409</v>
       </c>
       <c r="B15" t="n">
-        <v>107123</v>
+        <v>104280</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2188,21 +2188,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2282,7 +2282,7 @@
         <v>129800367</v>
       </c>
       <c r="B16" t="n">
-        <v>98772</v>
+        <v>98775</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>129800403</v>
       </c>
       <c r="B17" t="n">
-        <v>107123</v>
+        <v>107126</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         <v>129800389</v>
       </c>
       <c r="B18" t="n">
-        <v>98772</v>
+        <v>98775</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>129800345</v>
       </c>
       <c r="B19" t="n">
-        <v>98828</v>
+        <v>98831</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>129800349</v>
       </c>
       <c r="B20" t="n">
-        <v>98796</v>
+        <v>98799</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>129800385</v>
       </c>
       <c r="B21" t="n">
-        <v>98772</v>
+        <v>98775</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>129800366</v>
       </c>
       <c r="B22" t="n">
-        <v>107123</v>
+        <v>107126</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 56687-2025 artfynd.xlsx
+++ b/artfynd/A 56687-2025 artfynd.xlsx
@@ -2075,10 +2075,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129800410</v>
+        <v>129800409</v>
       </c>
       <c r="B14" t="n">
-        <v>107126</v>
+        <v>104280</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2086,21 +2086,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2177,10 +2177,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129800409</v>
+        <v>129800410</v>
       </c>
       <c r="B15" t="n">
-        <v>104280</v>
+        <v>107126</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2188,21 +2188,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220164</v>
+        <v>221849</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2279,59 +2279,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129800367</v>
+        <v>129800403</v>
       </c>
       <c r="B16" t="n">
-        <v>98775</v>
+        <v>107126</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219798</v>
+        <v>221849</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Väntinge 2:1 (2) (A 56687-2025), Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>700469</v>
+        <v>700398</v>
       </c>
       <c r="R16" t="n">
-        <v>6365674</v>
+        <v>6365502</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2377,7 +2363,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med enstaka kalkblock.</t>
+          <t>Kalkbarrskog med enstaka kalkblock. Skogen tidigare plockhuggen med avverkningsstråk.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2395,45 +2381,59 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129800403</v>
+        <v>129800367</v>
       </c>
       <c r="B17" t="n">
-        <v>107126</v>
+        <v>98775</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221849</v>
+        <v>219798</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Väntinge 2:1 (2) (A 56687-2025), Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>700398</v>
+        <v>700469</v>
       </c>
       <c r="R17" t="n">
-        <v>6365502</v>
+        <v>6365674</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med enstaka kalkblock. Skogen tidigare plockhuggen med avverkningsstråk.</t>
+          <t>Kalkbarrskog med enstaka kalkblock.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>

--- a/artfynd/A 56687-2025 artfynd.xlsx
+++ b/artfynd/A 56687-2025 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>129800392</v>
       </c>
       <c r="B3" t="n">
-        <v>98831</v>
+        <v>98832</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         <v>129800376</v>
       </c>
       <c r="B4" t="n">
-        <v>98775</v>
+        <v>98776</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>129800360</v>
       </c>
       <c r="B5" t="n">
-        <v>98775</v>
+        <v>98776</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>129800414</v>
       </c>
       <c r="B6" t="n">
-        <v>98775</v>
+        <v>98776</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>129800400</v>
       </c>
       <c r="B7" t="n">
-        <v>98775</v>
+        <v>98776</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>129800387</v>
       </c>
       <c r="B8" t="n">
-        <v>98775</v>
+        <v>98776</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>129800363</v>
       </c>
       <c r="B9" t="n">
-        <v>98775</v>
+        <v>98776</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1621,10 +1621,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129800379</v>
+        <v>129800557</v>
       </c>
       <c r="B10" t="n">
-        <v>98775</v>
+        <v>96394</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,36 +1632,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219798</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1670,10 +1665,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>700431</v>
+        <v>700398</v>
       </c>
       <c r="R10" t="n">
-        <v>6365585</v>
+        <v>6365612</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1716,11 +1711,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog med enstaka kalkblock. Skogen tidigare plockhuggen med avverkningsstråk.</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1737,10 +1727,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129800557</v>
+        <v>129800379</v>
       </c>
       <c r="B11" t="n">
-        <v>96393</v>
+        <v>98776</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,31 +1738,36 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>219798</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1781,10 +1776,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>700398</v>
+        <v>700431</v>
       </c>
       <c r="R11" t="n">
-        <v>6365612</v>
+        <v>6365585</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1827,6 +1822,11 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med enstaka kalkblock. Skogen tidigare plockhuggen med avverkningsstråk.</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1846,7 +1846,7 @@
         <v>129800406</v>
       </c>
       <c r="B12" t="n">
-        <v>98775</v>
+        <v>98776</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>129800393</v>
       </c>
       <c r="B13" t="n">
-        <v>98775</v>
+        <v>98776</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,10 +2075,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129800409</v>
+        <v>129800410</v>
       </c>
       <c r="B14" t="n">
-        <v>104280</v>
+        <v>107127</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2086,21 +2086,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220164</v>
+        <v>221849</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2177,10 +2177,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129800410</v>
+        <v>129800409</v>
       </c>
       <c r="B15" t="n">
-        <v>107126</v>
+        <v>104281</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2188,21 +2188,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2282,7 +2282,7 @@
         <v>129800403</v>
       </c>
       <c r="B16" t="n">
-        <v>107126</v>
+        <v>107127</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         <v>129800367</v>
       </c>
       <c r="B17" t="n">
-        <v>98775</v>
+        <v>98776</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         <v>129800389</v>
       </c>
       <c r="B18" t="n">
-        <v>98775</v>
+        <v>98776</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>129800345</v>
       </c>
       <c r="B19" t="n">
-        <v>98831</v>
+        <v>98832</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>129800349</v>
       </c>
       <c r="B20" t="n">
-        <v>98799</v>
+        <v>98800</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2845,59 +2845,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129800385</v>
+        <v>129800366</v>
       </c>
       <c r="B21" t="n">
-        <v>98775</v>
+        <v>107127</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219798</v>
+        <v>221849</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Väntinge 2:1 (2) (A 56687-2025), Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>700433</v>
+        <v>700478</v>
       </c>
       <c r="R21" t="n">
-        <v>6365521</v>
+        <v>6365684</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2943,7 +2929,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med enstaka kalkblock. Skogen tidigare plockhuggen med avverkningsstråk.</t>
+          <t>Kalkbarrskog med enstaka kalkblock.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2961,45 +2947,59 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129800366</v>
+        <v>129800385</v>
       </c>
       <c r="B22" t="n">
-        <v>107126</v>
+        <v>98776</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221849</v>
+        <v>219798</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Väntinge 2:1 (2) (A 56687-2025), Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>700478</v>
+        <v>700433</v>
       </c>
       <c r="R22" t="n">
-        <v>6365684</v>
+        <v>6365521</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med enstaka kalkblock.</t>
+          <t>Kalkbarrskog med enstaka kalkblock. Skogen tidigare plockhuggen med avverkningsstråk.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>

--- a/artfynd/A 56687-2025 artfynd.xlsx
+++ b/artfynd/A 56687-2025 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>129800392</v>
       </c>
       <c r="B3" t="n">
-        <v>98832</v>
+        <v>98849</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         <v>129800376</v>
       </c>
       <c r="B4" t="n">
-        <v>98776</v>
+        <v>98793</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>129800360</v>
       </c>
       <c r="B5" t="n">
-        <v>98776</v>
+        <v>98793</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>129800414</v>
       </c>
       <c r="B6" t="n">
-        <v>98776</v>
+        <v>98793</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>129800400</v>
       </c>
       <c r="B7" t="n">
-        <v>98776</v>
+        <v>98793</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>129800387</v>
       </c>
       <c r="B8" t="n">
-        <v>98776</v>
+        <v>98793</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>129800363</v>
       </c>
       <c r="B9" t="n">
-        <v>98776</v>
+        <v>98793</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>129800557</v>
       </c>
       <c r="B10" t="n">
-        <v>96394</v>
+        <v>96411</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>129800379</v>
       </c>
       <c r="B11" t="n">
-        <v>98776</v>
+        <v>98793</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>129800406</v>
       </c>
       <c r="B12" t="n">
-        <v>98776</v>
+        <v>98793</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>129800393</v>
       </c>
       <c r="B13" t="n">
-        <v>98776</v>
+        <v>98793</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,10 +2075,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129800410</v>
+        <v>129800409</v>
       </c>
       <c r="B14" t="n">
-        <v>107127</v>
+        <v>104298</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2086,21 +2086,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2177,10 +2177,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129800409</v>
+        <v>129800410</v>
       </c>
       <c r="B15" t="n">
-        <v>104281</v>
+        <v>107144</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2188,21 +2188,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220164</v>
+        <v>221849</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2279,45 +2279,59 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129800403</v>
+        <v>129800367</v>
       </c>
       <c r="B16" t="n">
-        <v>107127</v>
+        <v>98793</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221849</v>
+        <v>219798</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Väntinge 2:1 (2) (A 56687-2025), Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>700398</v>
+        <v>700469</v>
       </c>
       <c r="R16" t="n">
-        <v>6365502</v>
+        <v>6365674</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2363,7 +2377,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med enstaka kalkblock. Skogen tidigare plockhuggen med avverkningsstråk.</t>
+          <t>Kalkbarrskog med enstaka kalkblock.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2381,59 +2395,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129800367</v>
+        <v>129800403</v>
       </c>
       <c r="B17" t="n">
-        <v>98776</v>
+        <v>107144</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219798</v>
+        <v>221849</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Väntinge 2:1 (2) (A 56687-2025), Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>700469</v>
+        <v>700398</v>
       </c>
       <c r="R17" t="n">
-        <v>6365674</v>
+        <v>6365502</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med enstaka kalkblock.</t>
+          <t>Kalkbarrskog med enstaka kalkblock. Skogen tidigare plockhuggen med avverkningsstråk.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2500,7 +2500,7 @@
         <v>129800389</v>
       </c>
       <c r="B18" t="n">
-        <v>98776</v>
+        <v>98793</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>129800345</v>
       </c>
       <c r="B19" t="n">
-        <v>98832</v>
+        <v>98849</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>129800349</v>
       </c>
       <c r="B20" t="n">
-        <v>98800</v>
+        <v>98817</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>129800366</v>
       </c>
       <c r="B21" t="n">
-        <v>107127</v>
+        <v>107144</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>129800385</v>
       </c>
       <c r="B22" t="n">
-        <v>98776</v>
+        <v>98793</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 56687-2025 artfynd.xlsx
+++ b/artfynd/A 56687-2025 artfynd.xlsx
@@ -809,10 +809,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129800360</v>
+        <v>129800392</v>
       </c>
       <c r="B3" t="n">
-        <v>98809</v>
+        <v>98867</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,26 +820,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219798</v>
+        <v>219874</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -858,10 +858,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>700467</v>
+        <v>700427</v>
       </c>
       <c r="R3" t="n">
-        <v>6365717</v>
+        <v>6365490</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -907,7 +907,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med enstaka kalkblock.</t>
+          <t>Kalkbarrskog med enstaka kalkblock. Skogen tidigare plockhuggen med avverkningsstråk.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129800414</v>
+        <v>129800376</v>
       </c>
       <c r="B4" t="n">
-        <v>98809</v>
+        <v>98811</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -974,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>700392</v>
+        <v>700451</v>
       </c>
       <c r="R4" t="n">
-        <v>6365598</v>
+        <v>6365624</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med enstaka kalkblock. Skogen tidigare plockhuggen med avverkningsstråk.</t>
+          <t>Kalkbarrskog med enstaka kalkblock.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1041,10 +1041,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129800392</v>
+        <v>129800360</v>
       </c>
       <c r="B5" t="n">
-        <v>98865</v>
+        <v>98811</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1052,26 +1052,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219874</v>
+        <v>219798</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1090,10 +1090,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>700427</v>
+        <v>700467</v>
       </c>
       <c r="R5" t="n">
-        <v>6365490</v>
+        <v>6365717</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med enstaka kalkblock. Skogen tidigare plockhuggen med avverkningsstråk.</t>
+          <t>Kalkbarrskog med enstaka kalkblock.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1157,10 +1157,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129800376</v>
+        <v>129800414</v>
       </c>
       <c r="B6" t="n">
-        <v>98809</v>
+        <v>98811</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>700451</v>
+        <v>700392</v>
       </c>
       <c r="R6" t="n">
-        <v>6365624</v>
+        <v>6365598</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med enstaka kalkblock.</t>
+          <t>Kalkbarrskog med enstaka kalkblock. Skogen tidigare plockhuggen med avverkningsstråk.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1276,7 +1276,7 @@
         <v>129800400</v>
       </c>
       <c r="B7" t="n">
-        <v>98809</v>
+        <v>98811</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>129800387</v>
       </c>
       <c r="B8" t="n">
-        <v>98809</v>
+        <v>98811</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>129800363</v>
       </c>
       <c r="B9" t="n">
-        <v>98809</v>
+        <v>98811</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>129800557</v>
       </c>
       <c r="B10" t="n">
-        <v>96427</v>
+        <v>96429</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>129800379</v>
       </c>
       <c r="B11" t="n">
-        <v>98809</v>
+        <v>98811</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>129800406</v>
       </c>
       <c r="B12" t="n">
-        <v>98809</v>
+        <v>98811</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>129800393</v>
       </c>
       <c r="B13" t="n">
-        <v>98809</v>
+        <v>98811</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>129800409</v>
       </c>
       <c r="B14" t="n">
-        <v>104314</v>
+        <v>104316</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>129800410</v>
       </c>
       <c r="B15" t="n">
-        <v>107160</v>
+        <v>107163</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2279,59 +2279,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129800367</v>
+        <v>129800403</v>
       </c>
       <c r="B16" t="n">
-        <v>98809</v>
+        <v>107163</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219798</v>
+        <v>221849</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Väntinge 2:1 (2) (A 56687-2025), Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>700469</v>
+        <v>700398</v>
       </c>
       <c r="R16" t="n">
-        <v>6365674</v>
+        <v>6365502</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2377,7 +2363,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med enstaka kalkblock.</t>
+          <t>Kalkbarrskog med enstaka kalkblock. Skogen tidigare plockhuggen med avverkningsstråk.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2395,45 +2381,59 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129800403</v>
+        <v>129800367</v>
       </c>
       <c r="B17" t="n">
-        <v>107160</v>
+        <v>98811</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221849</v>
+        <v>219798</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Väntinge 2:1 (2) (A 56687-2025), Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>700398</v>
+        <v>700469</v>
       </c>
       <c r="R17" t="n">
-        <v>6365502</v>
+        <v>6365674</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med enstaka kalkblock. Skogen tidigare plockhuggen med avverkningsstråk.</t>
+          <t>Kalkbarrskog med enstaka kalkblock.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2500,7 +2500,7 @@
         <v>129800389</v>
       </c>
       <c r="B18" t="n">
-        <v>98809</v>
+        <v>98811</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>129800345</v>
       </c>
       <c r="B19" t="n">
-        <v>98865</v>
+        <v>98867</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>129800349</v>
       </c>
       <c r="B20" t="n">
-        <v>98833</v>
+        <v>98835</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>129800385</v>
       </c>
       <c r="B21" t="n">
-        <v>98809</v>
+        <v>98811</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>129800366</v>
       </c>
       <c r="B22" t="n">
-        <v>107160</v>
+        <v>107163</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
